--- a/robotai_BOM.xlsx
+++ b/robotai_BOM.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternatives" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2 - Full robot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Alternatives" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase 2 - Full robot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Phase 3 - Tools" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Screw sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,7 +583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>All prices CAD, read from the linked pages on 2026-09-25. 3D-printed parts excluded (printing covered). Blue cells = inputs (edit price/qty); totals recalc automatically.</t>
+          <t>All prices CAD, read from the linked pages on 2026-09-27. 3D-printed parts excluded (printing covered). Blue cells = inputs (edit price/qty); totals recalc automatically.</t>
         </is>
       </c>
     </row>
@@ -2758,4 +2760,1264 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 3 - Tools + last parts (in the Amazon.ca cart, NOT ordered yet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Checked with Kimi (senior build manager) on 2026-09-27: cut the crimper and breadboard, swapped the wrench set for one 13 mm wrench, added nylock nuts, files, sandpaper, knife, tweezers, fuses, switch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Product Name</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Unit Price (CAD)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Line Total (CAD)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Notes/Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Head camera (robot's live eyes)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>InnoMaker 1080P USB UVC camera, 130deg wide</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0CNCSFQC1</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13">
+        <f>D5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Board 38 x 38 mm, plugs into USB, no driver. Kimi: keep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Arm pivot bolts</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>M8 x 100 mm socket cap bolts, 10-pack</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07KRTHJZR</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>8 mm thick, 100 mm long. Shoulder, bicep, omoplate pivots (InMoov BOM: M8x100 x15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Lock nuts for the M8 bolts</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>M8 x 1.25 nylon-insert lock nuts, 20 pcs</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B075ZZY166</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>13 mm across. Stops the pivot bolts backing out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>13 mm wrench (for M8 nuts)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Sunex 13 mm combination wrench</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B00BNS8W2Q</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Only size the M8 nuts need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Ball race balls</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>6 mm 0.20 g airsoft BBs</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07T3K1TMS</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>6 mm balls. 31 per bicep race, 62+ for two arms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Grease for the ball races</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Super Lube 92003 silicone grease</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0081JE0OO</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>For the printed gears and races.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Joint position sensors</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>uxcell WH148 10k potentiometers, 10 pcs</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07JM62B3Q</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Shaft 6 mm. Pot relocated to the joint (InMoov mod).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Servo extension leads</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>30 cm 3-pin servo extension, 5 pcs</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07DMTYQ6N</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>30 cm each, 10 total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Wire joiners</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>WAGO 221 lever connectors, 25 pcs</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0BYBHYLG2</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Join power wires without soldering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Fuses</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>12 AWG inline fuse holders, 4 pcs</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0FDJYRGB7</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>10 A fuse on each power supply line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Main power switch</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Nilight rocker switch 20 A</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B06ZZHX6K3</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>One switch kills servo power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Screwdrivers</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>STREBITO 124-piece precision screwdriver set</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0968D5PSC</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Phillips PH0-PH2 + hex bits for M2-M4 screws.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Hex keys</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>GEARWRENCH 9-piece metric ball-end hex keys</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B098TYMJ3X</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>1.5-10 mm. Your countersunk kit: 2 mm = M3, 2.5 mm = M4. 6 mm = the M8 bolts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Pliers + cutter</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>SPEEDWOX mini long-nose pliers with cutter</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0CGHRCHP5</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="13">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Cheap single tool: grip + snip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Wire stripper</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Solsop self-adjusting wire stripper</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07XXMLFMV</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="13">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Strips 10-24 AWG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Soldering iron</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>60 W adjustable soldering iron kit</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B08K8VFTF9</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Cheapest decent kit (446 reviews).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Solder</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>TOWOT 63/37 rosin-core solder 0.8 mm</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0943TPRXK</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>0.8 mm wire, easy for beginners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Multimeter</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Digital multimeter</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07H65J7DQ</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="13">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Check PSU voltage before plugging servos in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Heat shrink</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>ASHINER heat shrink kit, 580 pcs</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B08XXGNJHG</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Covers solder joints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Calipers</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ADORIC digital caliper 0-150 mm</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07DFFYCXS</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Measure screws and printed parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Zip ties</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>400 assorted zip ties</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B08TVLYB3Q</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Cable management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Hot glue</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Surebonder LT-160 mini glue gun</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B004BPPHYE</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>InMoov wire management method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Needle files</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>10-piece needle file set</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B07PPYWSCY</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Fit printed parts (ball races, pistons). Kimi: day-1 blocker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Sandpaper</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>3M sandpaper 100/150/220 grit, 5 sheets</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B00004Z48U</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13">
+        <f>D28*E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Smooth printed parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Hobby knife</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>VViViD modelers knife + spare blades</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0CL5F9M4H</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Clean up prints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Tweezers</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NARZ 4-piece tweezers</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B09JLXKWB5</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Threading finger tendons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Safety glasses</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Clear safety glasses, 3-pack</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0F2JL22QN</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13">
+        <f>D31*E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>For cutting, soldering, springs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Subtotal (CAD, pre-tax)</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="16">
+        <f>SUM(F5:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>With HST 13%</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="16">
+        <f>F32*1.13</f>
+        <v/>
+      </c>
+      <c r="G33" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Screw sizes: what goes where</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Thick (mm)</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Long (mm)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Goes in</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>M8 x 100 mm bolt</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Shoulder, bicep, omoplate pivots - the arm hangs on these</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>6 mm hex key + 13 mm wrench</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>in cart</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>M8 x 60 mm bolt</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Elbow / forearm shaft only (too short for the shoulder)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>6 mm hex key + 13 mm wrench</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>ordered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>M4 x 20 mm bolt</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Joining printed parts together</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>2.5 mm hex key</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>ordered (DYWISHKEY kit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>M3 x 20 mm bolt</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Joining small printed parts</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>2 mm hex key</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>ordered (DYWISHKEY kit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>3.5 x 16 mm self-tapper</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Screwing servos into plastic (bicep build)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Phillips PH2</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>ordered (625 pc kit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>M2 x 8 mm self-tapper</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Servo horns, hand parts</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Phillips PH0/PH1</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>ordered (625 pc kit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>6 mm ball (BB)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Shoulder / bicep ball races, 31 per race</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>grease</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>in cart</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/robotai_BOM.xlsx
+++ b/robotai_BOM.xlsx
@@ -2768,7 +2768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Checked with Kimi (senior build manager) on 2026-09-27: cut the crimper and breadboard, swapped the wrench set for one 13 mm wrench, added nylock nuts, files, sandpaper, knife, tweezers, fuses, switch.</t>
+          <t>Checked with Kimi (senior build manager) on 2026-09-27: cut the crimper and breadboard, swapped the wrench set for one 13 mm wrench, added nylock nuts, files, sandpaper, knife, tweezers, fuses, switch. Breadboard kit re-added at Hasan's request (Kimi had marked it optional).</t>
         </is>
       </c>
     </row>
@@ -3403,28 +3403,28 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Check PSU voltage before plugging servos in.</t>
+          <t>Must-have: check each power supply's voltage before plugging servos in (12 V by mistake burns 6 V servos).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Heat shrink</t>
+          <t>Breadboards + jumper wires</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>ASHINER heat shrink kit, 580 pcs</t>
+          <t>830 + 400 point breadboards with jumper wire kit</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08XXGNJHG</t>
+          <t>https://www.amazon.ca/dp/B0BMFXPSVG</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>14.99</v>
+        <v>19.99</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>1</v>
@@ -3435,28 +3435,28 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Covers solder joints.</t>
+          <t>Test sensors/servo signals before soldering. Kimi said optional; re-added because Hasan asked.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Calipers</t>
+          <t>Heat shrink</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>ADORIC digital caliper 0-150 mm</t>
+          <t>ASHINER heat shrink kit, 580 pcs</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07DFFYCXS</t>
+          <t>https://www.amazon.ca/dp/B08XXGNJHG</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>11.43</v>
+        <v>14.99</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1</v>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Measure screws and printed parts.</t>
+          <t>Covers solder joints.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Zip ties</t>
+          <t>Calipers</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>400 assorted zip ties</t>
+          <t>ADORIC digital caliper 0-150 mm</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08TVLYB3Q</t>
+          <t>https://www.amazon.ca/dp/B07DFFYCXS</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>11.98</v>
+        <v>11.43</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>1</v>
@@ -3499,28 +3499,28 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Cable management.</t>
+          <t>Measure screws and printed parts.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Hot glue</t>
+          <t>Zip ties</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Surebonder LT-160 mini glue gun</t>
+          <t>400 assorted zip ties</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B004BPPHYE</t>
+          <t>https://www.amazon.ca/dp/B08TVLYB3Q</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>7.47</v>
+        <v>11.98</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1</v>
@@ -3531,28 +3531,28 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>InMoov wire management method.</t>
+          <t>Cable management.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Needle files</t>
+          <t>Hot glue</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>10-piece needle file set</t>
+          <t>Surebonder LT-160 mini glue gun</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07PPYWSCY</t>
+          <t>https://www.amazon.ca/dp/B004BPPHYE</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>9.99</v>
+        <v>7.47</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1</v>
@@ -3563,28 +3563,28 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Fit printed parts (ball races, pistons). Kimi: day-1 blocker.</t>
+          <t>InMoov wire management method.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Sandpaper</t>
+          <t>Needle files</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>3M sandpaper 100/150/220 grit, 5 sheets</t>
+          <t>10-piece needle file set</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B00004Z48U</t>
+          <t>https://www.amazon.ca/dp/B07PPYWSCY</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>7.97</v>
+        <v>9.99</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1</v>
@@ -3595,28 +3595,28 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Smooth printed parts.</t>
+          <t>Fit printed parts (ball races, pistons). Kimi: day-1 blocker.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Hobby knife</t>
+          <t>Sandpaper</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>VViViD modelers knife + spare blades</t>
+          <t>3M sandpaper 100/150/220 grit, 5 sheets</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0CL5F9M4H</t>
+          <t>https://www.amazon.ca/dp/B00004Z48U</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1</v>
@@ -3627,28 +3627,28 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Clean up prints.</t>
+          <t>Smooth printed parts.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Tweezers</t>
+          <t>Hobby knife</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>NARZ 4-piece tweezers</t>
+          <t>VViViD modelers knife + spare blades</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B09JLXKWB5</t>
+          <t>https://www.amazon.ca/dp/B0CL5F9M4H</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>6.29</v>
+        <v>7.98</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1</v>
@@ -3659,28 +3659,28 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Threading finger tendons.</t>
+          <t>Clean up prints.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Safety glasses</t>
+          <t>Tweezers</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Clear safety glasses, 3-pack</t>
+          <t>NARZ 4-piece tweezers</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0F2JL22QN</t>
+          <t>https://www.amazon.ca/dp/B09JLXKWB5</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>13.49</v>
+        <v>6.29</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>1</v>
@@ -3691,30 +3691,46 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
+          <t>Threading finger tendons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Safety glasses</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Clear safety glasses, 3-pack</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0F2JL22QN</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="13">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
           <t>For cutting, soldering, springs.</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Subtotal (CAD, pre-tax)</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="16">
-        <f>SUM(F5:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>With HST 13%</t>
+          <t>Subtotal (CAD, pre-tax)</t>
         </is>
       </c>
       <c r="B33" s="15" t="n"/>
@@ -3722,14 +3738,30 @@
       <c r="D33" s="15" t="n"/>
       <c r="E33" s="15" t="n"/>
       <c r="F33" s="16">
-        <f>F32*1.13</f>
+        <f>SUM(F5:F32)</f>
         <v/>
       </c>
       <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>With HST 13%</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="16">
+        <f>F33*1.13</f>
+        <v/>
+      </c>
+      <c r="G34" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A33:E33"/>
   </mergeCells>
   <hyperlinks>
@@ -3760,6 +3792,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/robotai_BOM.xlsx
+++ b/robotai_BOM.xlsx
@@ -2768,7 +2768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2790,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Checked with Kimi (senior build manager) on 2026-09-27: cut the crimper and breadboard, swapped the wrench set for one 13 mm wrench, added nylock nuts, files, sandpaper, knife, tweezers, fuses, switch. Breadboard kit re-added at Hasan's request (Kimi had marked it optional).</t>
+          <t>Checked with Kimi (senior build manager) on 2026-09-27: cut the crimper and breadboard, swapped the wrench set for one 13 mm wrench, added nylock nuts, files, sandpaper, knife, tweezers, fuses, switch. Breadboard kit re-added at Hasan's request (Kimi had marked it optional). Recheck vs orders: the DC barrel-to-screw adapters from Phase 1 were never ordered; added.</t>
         </is>
       </c>
     </row>
@@ -3090,21 +3090,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Wire joiners</t>
+          <t>Power plug adapters (PSU to boards)</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>WAGO 221 lever connectors, 25 pcs</t>
+          <t>20 pcs 5.5 x 2.1 mm DC barrel to screw terminal</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0BYBHYLG2</t>
+          <t>https://www.amazon.ca/dp/B0C4JJ2HB4</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>29.39</v>
+        <v>11.99</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>1</v>
@@ -3115,28 +3115,28 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Join power wires without soldering.</t>
+          <t>Was in the Phase 1 plan but never ordered. Connects the 2 power supplies to the PCA9685 servo boards.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Fuses</t>
+          <t>Wire joiners</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>12 AWG inline fuse holders, 4 pcs</t>
+          <t>WAGO 221 lever connectors, 25 pcs</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0FDJYRGB7</t>
+          <t>https://www.amazon.ca/dp/B0BYBHYLG2</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>9.99</v>
+        <v>29.39</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>1</v>
@@ -3147,28 +3147,28 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>10 A fuse on each power supply line.</t>
+          <t>Join power wires without soldering.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Main power switch</t>
+          <t>Fuses</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Nilight rocker switch 20 A</t>
+          <t>12 AWG inline fuse holders, 4 pcs</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B06ZZHX6K3</t>
+          <t>https://www.amazon.ca/dp/B0FDJYRGB7</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>4.62</v>
+        <v>9.99</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>1</v>
@@ -3179,28 +3179,28 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>One switch kills servo power.</t>
+          <t>10 A fuse on each power supply line.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Screwdrivers</t>
+          <t>Main power switch</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>STREBITO 124-piece precision screwdriver set</t>
+          <t>Nilight rocker switch 20 A</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0968D5PSC</t>
+          <t>https://www.amazon.ca/dp/B06ZZHX6K3</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>25.99</v>
+        <v>4.62</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>1</v>
@@ -3211,28 +3211,28 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Phillips PH0-PH2 + hex bits for M2-M4 screws.</t>
+          <t>One switch kills servo power.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Hex keys</t>
+          <t>Screwdrivers</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>GEARWRENCH 9-piece metric ball-end hex keys</t>
+          <t>STREBITO 124-piece precision screwdriver set</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B098TYMJ3X</t>
+          <t>https://www.amazon.ca/dp/B0968D5PSC</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>10.99</v>
+        <v>25.99</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>1</v>
@@ -3243,28 +3243,28 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>1.5-10 mm. Your countersunk kit: 2 mm = M3, 2.5 mm = M4. 6 mm = the M8 bolts.</t>
+          <t>Phillips PH0-PH2 + hex bits for M2-M4 screws.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Pliers + cutter</t>
+          <t>Hex keys</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SPEEDWOX mini long-nose pliers with cutter</t>
+          <t>GEARWRENCH 9-piece metric ball-end hex keys</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0CGHRCHP5</t>
+          <t>https://www.amazon.ca/dp/B098TYMJ3X</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>9.69</v>
+        <v>10.99</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1</v>
@@ -3275,28 +3275,28 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Cheap single tool: grip + snip.</t>
+          <t>1.5-10 mm. Your countersunk kit: 2 mm = M3, 2.5 mm = M4. 6 mm = the M8 bolts.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Wire stripper</t>
+          <t>Pliers + cutter</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Solsop self-adjusting wire stripper</t>
+          <t>SPEEDWOX mini long-nose pliers with cutter</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07XXMLFMV</t>
+          <t>https://www.amazon.ca/dp/B0CGHRCHP5</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>10.19</v>
+        <v>9.69</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>1</v>
@@ -3307,28 +3307,28 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Strips 10-24 AWG.</t>
+          <t>Cheap single tool: grip + snip.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Soldering iron</t>
+          <t>Wire stripper</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>60 W adjustable soldering iron kit</t>
+          <t>Solsop self-adjusting wire stripper</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08K8VFTF9</t>
+          <t>https://www.amazon.ca/dp/B07XXMLFMV</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>13.99</v>
+        <v>10.19</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>1</v>
@@ -3339,28 +3339,28 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Cheapest decent kit (446 reviews).</t>
+          <t>Strips 10-24 AWG.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Solder</t>
+          <t>Soldering iron</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>TOWOT 63/37 rosin-core solder 0.8 mm</t>
+          <t>60 W adjustable soldering iron kit</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0943TPRXK</t>
+          <t>https://www.amazon.ca/dp/B08K8VFTF9</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>12.97</v>
+        <v>13.99</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>1</v>
@@ -3371,28 +3371,28 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>0.8 mm wire, easy for beginners.</t>
+          <t>Cheapest decent kit (446 reviews).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Multimeter</t>
+          <t>Solder</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Digital multimeter</t>
+          <t>TOWOT 63/37 rosin-core solder 0.8 mm</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07H65J7DQ</t>
+          <t>https://www.amazon.ca/dp/B0943TPRXK</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>19.98</v>
+        <v>12.97</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>1</v>
@@ -3403,28 +3403,28 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Must-have: check each power supply's voltage before plugging servos in (12 V by mistake burns 6 V servos).</t>
+          <t>0.8 mm wire, easy for beginners.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Breadboards + jumper wires</t>
+          <t>Multimeter</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>830 + 400 point breadboards with jumper wire kit</t>
+          <t>Digital multimeter</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0BMFXPSVG</t>
+          <t>https://www.amazon.ca/dp/B07H65J7DQ</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>19.99</v>
+        <v>19.98</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>1</v>
@@ -3435,28 +3435,28 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Test sensors/servo signals before soldering. Kimi said optional; re-added because Hasan asked.</t>
+          <t>Must-have: check each power supply's voltage before plugging servos in (12 V by mistake burns 6 V servos).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Heat shrink</t>
+          <t>Breadboards + jumper wires</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>ASHINER heat shrink kit, 580 pcs</t>
+          <t>830 + 400 point breadboards with jumper wire kit</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08XXGNJHG</t>
+          <t>https://www.amazon.ca/dp/B0BMFXPSVG</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14.99</v>
+        <v>19.99</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1</v>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Covers solder joints.</t>
+          <t>Test sensors/servo signals before soldering. Kimi said optional; re-added because Hasan asked.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Calipers</t>
+          <t>Heat shrink</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ADORIC digital caliper 0-150 mm</t>
+          <t>ASHINER heat shrink kit, 580 pcs</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07DFFYCXS</t>
+          <t>https://www.amazon.ca/dp/B08XXGNJHG</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>11.43</v>
+        <v>14.99</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>1</v>
@@ -3499,28 +3499,28 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Measure screws and printed parts.</t>
+          <t>Covers solder joints.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Zip ties</t>
+          <t>Calipers</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>400 assorted zip ties</t>
+          <t>ADORIC digital caliper 0-150 mm</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B08TVLYB3Q</t>
+          <t>https://www.amazon.ca/dp/B07DFFYCXS</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>11.98</v>
+        <v>11.43</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1</v>
@@ -3531,28 +3531,28 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Cable management.</t>
+          <t>Measure screws and printed parts.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Hot glue</t>
+          <t>Zip ties</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Surebonder LT-160 mini glue gun</t>
+          <t>400 assorted zip ties</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B004BPPHYE</t>
+          <t>https://www.amazon.ca/dp/B08TVLYB3Q</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>7.47</v>
+        <v>11.98</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>1</v>
@@ -3563,28 +3563,28 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>InMoov wire management method.</t>
+          <t>Cable management.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Needle files</t>
+          <t>Hot glue</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>10-piece needle file set</t>
+          <t>Surebonder LT-160 mini glue gun</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B07PPYWSCY</t>
+          <t>https://www.amazon.ca/dp/B004BPPHYE</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>9.99</v>
+        <v>7.47</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>1</v>
@@ -3595,28 +3595,28 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Fit printed parts (ball races, pistons). Kimi: day-1 blocker.</t>
+          <t>InMoov wire management method.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Sandpaper</t>
+          <t>Needle files</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>3M sandpaper 100/150/220 grit, 5 sheets</t>
+          <t>10-piece needle file set</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B00004Z48U</t>
+          <t>https://www.amazon.ca/dp/B07PPYWSCY</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>7.97</v>
+        <v>9.99</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>1</v>
@@ -3627,28 +3627,28 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Smooth printed parts.</t>
+          <t>Fit printed parts (ball races, pistons). Kimi: day-1 blocker.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Hobby knife</t>
+          <t>Sandpaper</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>VViViD modelers knife + spare blades</t>
+          <t>3M sandpaper 100/150/220 grit, 5 sheets</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0CL5F9M4H</t>
+          <t>https://www.amazon.ca/dp/B00004Z48U</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>1</v>
@@ -3659,28 +3659,28 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Clean up prints.</t>
+          <t>Smooth printed parts.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Tweezers</t>
+          <t>Hobby knife</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>NARZ 4-piece tweezers</t>
+          <t>VViViD modelers knife + spare blades</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B09JLXKWB5</t>
+          <t>https://www.amazon.ca/dp/B0CL5F9M4H</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>6.29</v>
+        <v>7.98</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>1</v>
@@ -3691,28 +3691,28 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Threading finger tendons.</t>
+          <t>Clean up prints.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Safety glasses</t>
+          <t>Tweezers</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Clear safety glasses, 3-pack</t>
+          <t>NARZ 4-piece tweezers</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>https://www.amazon.ca/dp/B0F2JL22QN</t>
+          <t>https://www.amazon.ca/dp/B09JLXKWB5</t>
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>13.49</v>
+        <v>6.29</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>1</v>
@@ -3723,30 +3723,46 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
+          <t>Threading finger tendons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Safety glasses</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Clear safety glasses, 3-pack</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.ca/dp/B0F2JL22QN</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
           <t>For cutting, soldering, springs.</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Subtotal (CAD, pre-tax)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="16">
-        <f>SUM(F5:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>With HST 13%</t>
+          <t>Subtotal (CAD, pre-tax)</t>
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
@@ -3754,15 +3770,31 @@
       <c r="D34" s="15" t="n"/>
       <c r="E34" s="15" t="n"/>
       <c r="F34" s="16">
-        <f>F33*1.13</f>
+        <f>SUM(F5:F33)</f>
         <v/>
       </c>
       <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>With HST 13%</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="16">
+        <f>F34*1.13</f>
+        <v/>
+      </c>
+      <c r="G35" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A35:E35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
@@ -3793,6 +3825,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
